--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/NEW_JERSEY_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/NEW_JERSEY_2016.xlsx
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C211">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C605">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C644">
@@ -15979,7 +15979,7 @@
         <v>148</v>
       </c>
       <c r="D868">
-        <v>0.009706190975865687</v>
+        <v>0.009706190975865689</v>
       </c>
     </row>
     <row r="869">
